--- a/utils/monday_sprint_sprint_2024-34.xlsx
+++ b/utils/monday_sprint_sprint_2024-34.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="146">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>25409</t>
+    <t>6446651537</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>12/04/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>27/04/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,19 +102,25 @@
     <t>Abril</t>
   </si>
   <si>
-    <t>25415</t>
+    <t>6446636727</t>
   </si>
   <si>
     <t>Tempo Sic</t>
   </si>
   <si>
-    <t>25405</t>
+    <t>23/04/2024</t>
+  </si>
+  <si>
+    <t>6446665368</t>
   </si>
   <si>
     <t>Pendencia Portal</t>
   </si>
   <si>
-    <t>25396</t>
+    <t>22/04/2024</t>
+  </si>
+  <si>
+    <t>6446701992</t>
   </si>
   <si>
     <t>Consulta ordens de compra de investimentos</t>
@@ -123,19 +129,28 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>25569</t>
+    <t>18/04/2024</t>
+  </si>
+  <si>
+    <t>6446271212</t>
   </si>
   <si>
     <t>SUGESTÃO APONTAMENTO ELETRÔNICO - ESCARFAGEM REB. VI - ACRESCENTAR LINHA DE RETRABALHO DE ESCARFAGEM/ ESCARFAGEM CONC. USINADO!</t>
   </si>
   <si>
-    <t>25573</t>
+    <t>21/04/2024</t>
+  </si>
+  <si>
+    <t>6446229888</t>
   </si>
   <si>
     <t>Excel modelos programados na moldagem</t>
   </si>
   <si>
-    <t>24509</t>
+    <t>17/04/2024</t>
+  </si>
+  <si>
+    <t>6036723635</t>
   </si>
   <si>
     <t>LIBERAR PERFIL DE ACESSO WMS EXPEDIÇÃO</t>
@@ -144,10 +159,13 @@
     <t>09/02/2024</t>
   </si>
   <si>
+    <t>28/04/2024</t>
+  </si>
+  <si>
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>25616</t>
+    <t>6463372831</t>
   </si>
   <si>
     <t>Ajustes no sistema para a programação em horas</t>
@@ -159,61 +177,64 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>25375</t>
+    <t>6446721093</t>
   </si>
   <si>
     <t>Valor do estoque Família</t>
   </si>
   <si>
-    <t>25568</t>
+    <t>6446285512</t>
   </si>
   <si>
     <t>SUGESTÃO DO APONTAMENTO ELETRÔNICO - AJUSTAGEM REBARBAÇÃO VII - ACRESCENTAR LINHA DE RETRABALHO DE AJUSTAGEM FINAL!</t>
   </si>
   <si>
-    <t>24929</t>
+    <t>6446768296</t>
   </si>
   <si>
     <t>Relatório de processos</t>
   </si>
   <si>
-    <t>25168</t>
+    <t>6446757271</t>
   </si>
   <si>
     <t>Planilhão do Pré-produtivo</t>
   </si>
   <si>
-    <t>25510</t>
+    <t>6446348472</t>
   </si>
   <si>
     <t>Melhoria relatório de movimentação</t>
   </si>
   <si>
-    <t>25356</t>
+    <t>6446742619</t>
   </si>
   <si>
     <t>QlikSense - campos</t>
   </si>
   <si>
-    <t>25533</t>
+    <t>25/04/2024</t>
+  </si>
+  <si>
+    <t>6446337610</t>
   </si>
   <si>
     <t>Sistema Manutenção</t>
   </si>
   <si>
-    <t>25506</t>
+    <t>6446381202</t>
   </si>
   <si>
     <t>Relatório sistema de corridas</t>
   </si>
   <si>
-    <t>25478</t>
+    <t>6446448331</t>
   </si>
   <si>
     <t>Sequências com corridas cadastrada</t>
   </si>
   <si>
-    <t>25266</t>
+    <t>6347481413</t>
   </si>
   <si>
     <t>Add Perguntas na MPO - Usinagem</t>
@@ -228,109 +249,109 @@
     <t>Março</t>
   </si>
   <si>
-    <t>25481</t>
+    <t>6446413040</t>
   </si>
   <si>
     <t>Relatório de performance por setor</t>
   </si>
   <si>
-    <t>25250</t>
+    <t>6347492399</t>
   </si>
   <si>
     <t>Registro de macharia incompleto - Verificar Bug</t>
   </si>
   <si>
-    <t>25442</t>
+    <t>6446532602</t>
   </si>
   <si>
     <t>REMOÇÃO DO CAMPO POSIÇÃO NOS DESENHOS 3D</t>
   </si>
   <si>
-    <t>25578</t>
+    <t>6446194571</t>
   </si>
   <si>
     <t>Eliminação de Volume automático</t>
   </si>
   <si>
-    <t>25437</t>
+    <t>6446546359</t>
   </si>
   <si>
     <t>Abertura de chamado para Relatório de MRP de materiais no CPP</t>
   </si>
   <si>
-    <t>25418</t>
+    <t>6446619303</t>
   </si>
   <si>
     <t>Melhoria no sistema de Liberação de ensaios e Ensaios destrutivos</t>
   </si>
   <si>
-    <t>25590</t>
+    <t>6446166500</t>
   </si>
   <si>
     <t>Cálculo do carbono equivalente nas corridas</t>
   </si>
   <si>
-    <t>25580</t>
+    <t>6446185681</t>
   </si>
   <si>
     <t>Pçs sem Pedido &gt; constar no MPS</t>
   </si>
   <si>
-    <t>25423</t>
+    <t>6446594869</t>
   </si>
   <si>
     <t>Melhoria do preenchimento de Análise Química no AP119</t>
   </si>
   <si>
-    <t>25425</t>
+    <t>6446581722</t>
   </si>
   <si>
     <t>Estorno de refugo - Observação</t>
   </si>
   <si>
-    <t>25416</t>
+    <t>6446628161</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DO FLUXO 105 E DEPENDÊNCIAS</t>
   </si>
   <si>
-    <t>25618</t>
+    <t>6463366480</t>
   </si>
   <si>
     <t>Melhorias na portaria fiscal</t>
   </si>
   <si>
-    <t>25577</t>
+    <t>6466620127</t>
   </si>
   <si>
     <t>Bloqueio de exclusão do 7273 - avaliação de amostra</t>
   </si>
   <si>
-    <t>24556</t>
+    <t>6467620620</t>
   </si>
   <si>
     <t>Controle de Período Firme - Inconsistencias - Homologação</t>
   </si>
   <si>
-    <t>25326</t>
+    <t>6467806803</t>
   </si>
   <si>
     <t>Pendência Automática</t>
   </si>
   <si>
-    <t>21782</t>
+    <t>6467871930</t>
   </si>
   <si>
     <t>Diferença - Estoque Processo</t>
   </si>
   <si>
-    <t>25104</t>
+    <t>6468038550</t>
   </si>
   <si>
     <t>Ordenar aplicações do QSense</t>
   </si>
   <si>
-    <t>25303</t>
+    <t>6347420246</t>
   </si>
   <si>
     <t>Inclusão de Modal - Sistema de Invoice</t>
@@ -342,7 +363,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-34</t>
+    <t>Fev/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -990,7 +1011,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1007,7 +1028,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1019,10 +1040,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1037,7 +1058,7 @@
         <v>23</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1054,7 +1075,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1066,13 +1087,13 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>21</v>
@@ -1084,7 +1105,7 @@
         <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1101,7 +1122,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1113,10 +1134,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1131,7 +1152,7 @@
         <v>23</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1148,7 +1169,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1160,10 +1181,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1178,7 +1199,7 @@
         <v>23</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1195,7 +1216,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1207,10 +1228,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1222,10 +1243,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1237,12 +1258,12 @@
         <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1254,13 +1275,13 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
@@ -1269,10 +1290,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1281,7 +1302,7 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1289,7 +1310,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1301,10 +1322,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1319,7 +1340,7 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1336,7 +1357,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1348,10 +1369,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1366,7 +1387,7 @@
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1383,7 +1404,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1395,10 +1416,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1413,7 +1434,7 @@
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1430,7 +1451,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1442,13 +1463,13 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>21</v>
@@ -1477,7 +1498,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1489,13 +1510,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>21</v>
@@ -1507,7 +1528,7 @@
         <v>23</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1524,7 +1545,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1536,10 +1557,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1554,7 +1575,7 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1571,7 +1592,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1583,10 +1604,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1601,7 +1622,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1618,7 +1639,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1630,10 +1651,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1648,7 +1669,7 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1665,7 +1686,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1677,10 +1698,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1695,7 +1716,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1712,7 +1733,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1724,10 +1745,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1739,10 +1760,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1751,15 +1772,15 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1771,10 +1792,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1789,7 +1810,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1806,7 +1827,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1818,10 +1839,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1833,10 +1854,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1845,15 +1866,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1865,10 +1886,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1883,7 +1904,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1900,7 +1921,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1912,10 +1933,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1930,7 +1951,7 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1947,7 +1968,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1959,10 +1980,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1977,7 +1998,7 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1994,7 +2015,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2006,10 +2027,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2024,7 +2045,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2041,7 +2062,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2053,10 +2074,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2071,7 +2092,7 @@
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2088,7 +2109,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2100,10 +2121,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2135,7 +2156,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2147,10 +2168,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2182,7 +2203,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2194,10 +2215,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2229,7 +2250,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2241,10 +2262,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2276,7 +2297,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2288,13 +2309,13 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>21</v>
@@ -2303,10 +2324,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2315,7 +2336,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2323,7 +2344,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2335,10 +2356,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2350,10 +2371,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2362,7 +2383,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -2370,7 +2391,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2382,13 +2403,13 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>21</v>
@@ -2397,10 +2418,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2409,7 +2430,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2417,7 +2438,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2429,10 +2450,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2444,10 +2465,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2456,7 +2477,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2464,7 +2485,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2476,13 +2497,13 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>21</v>
@@ -2491,10 +2512,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2503,7 +2524,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2511,7 +2532,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2523,10 +2544,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2538,10 +2559,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2550,7 +2571,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2558,7 +2579,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2570,10 +2591,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2585,10 +2606,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2597,10 +2618,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2616,23 +2637,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2640,16 +2661,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2660,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2668,7 +2689,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2681,7 +2702,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2689,7 +2710,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2720,12 +2741,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B2">
         <v>36</v>
@@ -2739,7 +2760,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2749,25 +2770,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2784,13 +2805,13 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2802,15 +2823,15 @@
         <v>36</v>
       </c>
       <c r="P10" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="Q10">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H11">
         <v>7</v>
@@ -2822,19 +2843,19 @@
         <v>36</v>
       </c>
       <c r="M11" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="Q11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="7:17" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G12" t="s">
         <v>20</v>
       </c>
@@ -2842,33 +2863,27 @@
         <v>29</v>
       </c>
       <c r="J12" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
-      <c r="P12" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q12">
-        <v>3</v>
-      </c>
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2876,13 +2891,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2890,7 +2905,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2898,7 +2913,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2906,7 +2921,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2914,10 +2929,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2925,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2933,142 +2948,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
